--- a/01-INTRO/M03/CAT Activity - FactSet.xlsx
+++ b/01-INTRO/M03/CAT Activity - FactSet.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailendicott-my.sharepoint.com/personal/bevitts_endicott_edu/Documents/BUS311 Corporate Finance/BME - FA25- Teaching Materials - Brealey/Chapter 3- Accounting and Finance/CAT - Class Activity/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bethanyevittsair2/Documents/GitHub/BUS311-Corporate_Finance/01-INTRO/M03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{0629CC27-16BE-4C8B-85CF-314FD6492C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A72C73A5-CD8A-4765-B6CF-9224FAD78029}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA35F50-76EE-134F-A3E9-2CC1EDC376C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0347E573-4F0D-418B-B17B-965F803E2356}"/>
+    <workbookView xWindow="6600" yWindow="600" windowWidth="30440" windowHeight="20040" xr2:uid="{0347E573-4F0D-418B-B17B-965F803E2356}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Student CAT Wksht" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>CAT</t>
   </si>
@@ -79,9 +79,6 @@
     <t>Data Type</t>
   </si>
   <si>
-    <t xml:space="preserve">                                                                       {Company Overview}</t>
-  </si>
-  <si>
     <t>Ticker</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
   </si>
   <si>
     <t>52 Week Low</t>
-  </si>
-  <si>
-    <t>COGS (Calculation)</t>
   </si>
   <si>
     <t>52 Week High</t>
@@ -164,39 +158,21 @@
     </r>
   </si>
   <si>
-    <t>Net Working Capital</t>
-  </si>
-  <si>
     <t>Total Shareholders Equity</t>
   </si>
   <si>
     <t>Start</t>
   </si>
   <si>
-    <t>Earning Per Share</t>
-  </si>
-  <si>
     <t>End</t>
   </si>
   <si>
     <t>Check</t>
   </si>
   <si>
-    <t>Asset = Liabilities +Owners Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Using FactSet </t>
-  </si>
-  <si>
-    <t>All the information in the green cells</t>
-  </si>
-  <si>
     <t>Free Cash Flow Analysis</t>
   </si>
   <si>
-    <t>Calculate all the information in the blue cells</t>
-  </si>
-  <si>
     <t>Net Cash Flow from Operations</t>
   </si>
   <si>
@@ -206,116 +182,82 @@
     <t>Net Financing Cash Flow</t>
   </si>
   <si>
-    <t>Free Cash Flow</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">% </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Georgia Pro"/>
-        <family val="1"/>
-      </rPr>
-      <t>∆</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 21 to 22</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">% </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Georgia Pro"/>
-        <family val="1"/>
-      </rPr>
-      <t>∆</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 22 to 23</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">% </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Georgia Pro"/>
-        <family val="1"/>
-      </rPr>
-      <t>∆</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 23 to 24</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">% </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Georgia Pro"/>
-        <family val="1"/>
-      </rPr>
-      <t>∆</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 24 to 25</t>
-    </r>
-  </si>
-  <si>
-    <t>Cells in gray are not yet available</t>
-  </si>
-  <si>
-    <t>Find</t>
-  </si>
-  <si>
-    <t>years</t>
+    <t>Company Overview</t>
+  </si>
+  <si>
+    <t>Analysis Period</t>
+  </si>
+  <si>
+    <t>Year-over-Year Growth</t>
+  </si>
+  <si>
+    <t>2021 to 2022</t>
+  </si>
+  <si>
+    <t>2022 to 2023</t>
+  </si>
+  <si>
+    <t>2023 to 2024</t>
+  </si>
+  <si>
+    <t>2024 to 2025</t>
+  </si>
+  <si>
+    <t>COGS (excluding D&amp;A)</t>
+  </si>
+  <si>
+    <t>Change in Working Capital</t>
+  </si>
+  <si>
+    <t>Earnings Per Share</t>
+  </si>
+  <si>
+    <t>FactSet Data Retrieval</t>
+  </si>
+  <si>
+    <t>Student Task</t>
+  </si>
+  <si>
+    <t>Enter FactSet-sourced historical data in green cells.</t>
+  </si>
+  <si>
+    <t>Calculate blue cells using formulas; do not hardcode results.</t>
+  </si>
+  <si>
+    <t>Gray cells indicate data not yet available.</t>
+  </si>
+  <si>
+    <t>Capital Expenditures (cash paid)</t>
+  </si>
+  <si>
+    <t>Free Cash Flow (CFO - CapEx)</t>
+  </si>
+  <si>
+    <t>Net Change in Cash</t>
+  </si>
+  <si>
+    <t>Interpretation Questions</t>
+  </si>
+  <si>
+    <t>1. Did CAT outperform the S&amp;P 500 over the period? Support your answer with returns.</t>
+  </si>
+  <si>
+    <t>2. Explain the major drivers of revenue, EBITDA, and EPS trends.</t>
+  </si>
+  <si>
+    <t>3. Assess leverage using long-term debt and shareholders' equity.</t>
+  </si>
+  <si>
+    <t>4. Explain the difference between free cash flow and net change in cash.</t>
+  </si>
+  <si>
+    <t>Component gap: Assets - Liabilities - Equity</t>
+  </si>
+  <si>
+    <t>Review small gaps as rounding/classification differences.</t>
+  </si>
+  <si>
+    <t>Reported Assets = Reported Liabilities &amp; Equity</t>
   </si>
 </sst>
 </file>
@@ -324,14 +266,14 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="m/d/yy"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.0_);\(&quot;$&quot;#,##0.0\);&quot;$&quot;#,##0.0_);@_)"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\);&quot;$&quot;#,##0.00_);@_)"/>
-    <numFmt numFmtId="168" formatCode="0.0%_);\(0.0%\);0.0%_);@_)"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.0_);\(&quot;$&quot;#,##0.0\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0_);\(&quot;$&quot;#,##0.0\);&quot;$&quot;#,##0.0_);@_)"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\);&quot;$&quot;#,##0.00_);@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0%_);\(0.0%\);0.0%_);@_)"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.0_);\(&quot;$&quot;#,##0.0\)"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0;\(&quot;$&quot;#,##0\);\-"/>
+    <numFmt numFmtId="169" formatCode="0.0%;\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,20 +313,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Georgia Pro"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -465,8 +393,34 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -527,8 +481,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B2D5C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -751,15 +729,277 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF002856"/>
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF002856"/>
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF808080"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF0B2D5C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -768,7 +1008,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -778,83 +1018,177 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="10" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="17" fillId="11" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="13" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="12" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="13" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="13" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="13" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="13" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="168" fontId="19" fillId="13" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="22" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="19" fillId="13" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1312,32 +1646,55 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{28C2350C-2A62-414B-AD58-2E1C449BB493}">
+  <we:reference id="wa200010215" version="2.0.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010215" version="2.0.0.0" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="bps.codex_control.document_id" value="&quot;81e1a09a-0cd6-4f4d-8ca3-eaa802cebf96&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BA63DB5-F339-44CF-94CD-D29E20CB87E9}">
-  <dimension ref="A1:N30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="2" max="2" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.6640625" customWidth="1"/>
+    <col min="5" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="14.1640625" customWidth="1"/>
+    <col min="12" max="12" width="15.5" customWidth="1"/>
+    <col min="13" max="13" width="13.1640625" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K1" s="52" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K1" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="49"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="D2" s="4" t="s">
@@ -1347,513 +1704,608 @@
         <f>B19</f>
         <v>44561</v>
       </c>
-      <c r="F2" s="6">
-        <f>E2+365</f>
+      <c r="F2" s="48">
+        <f>DATE(YEAR(E2)+1,12,31)</f>
         <v>44926</v>
       </c>
-      <c r="G2" s="6">
-        <f t="shared" ref="G2:I2" si="0">F2+365</f>
+      <c r="G2" s="48">
+        <f>DATE(YEAR(F2)+1,12,31)</f>
         <v>45291</v>
       </c>
-      <c r="H2" s="6">
-        <f t="shared" si="0"/>
-        <v>45656</v>
-      </c>
-      <c r="I2" s="6">
-        <f t="shared" si="0"/>
-        <v>46021</v>
-      </c>
-      <c r="K2" s="6" t="s">
+      <c r="H2" s="48">
+        <f>DATE(YEAR(G2)+1,12,31)</f>
+        <v>45657</v>
+      </c>
+      <c r="I2" s="48">
+        <f>DATE(YEAR(H2)+1,12,31)</f>
+        <v>46022</v>
+      </c>
+      <c r="K2" s="51" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="51" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="83"/>
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="D5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="27"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="27"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="D6" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="27"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="27"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="D7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="28"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="28"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="D8" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="28"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="28"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="15"/>
+      <c r="D9" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="27"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="27"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="D10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="28"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="28"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="D11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="28"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="28"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="D12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="29"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="D13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="27"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="27"/>
+    </row>
+    <row r="14" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="21"/>
+      <c r="D14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="27"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="D15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="27"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="27"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="D16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="27"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="27"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="30"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="30"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="44" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="27"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="27"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="45">
+        <v>44561</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="54"/>
-      <c r="D3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="13"/>
-      <c r="D5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="28"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="28"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="D6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="28"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="28"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="D7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="29"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="29"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="D8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="29"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="29"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="D9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="28"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="28"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="D10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="29"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="29"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="D11" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="29"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="29"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="20"/>
-      <c r="D12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="30"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="21"/>
-      <c r="D13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="28"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="28"/>
-    </row>
-    <row r="14" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="22"/>
-      <c r="D14" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="28"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="28"/>
-    </row>
-    <row r="15" spans="1:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="D15" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="28"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="28"/>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="25"/>
-      <c r="D16" s="11" t="s">
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="28"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="28"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="28"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="28"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D17" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="31"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="31"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="28"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="28"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="50">
-        <v>44561</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="29"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="29"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="50">
+      <c r="B20" s="45">
         <v>46022</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" t="str">
+        <f>IF(COUNTA(E13,E14,E18)&lt;3,"",E13-E14-E18)</f>
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <f>IF(COUNTA(F13,F14,F18)&lt;3,"",F13-F14-F18)</f>
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <f>IF(COUNTA(G13,G14,G18)&lt;3,"",G13-G14-G18)</f>
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <f>IF(COUNTA(H13,H14,H18)&lt;3,"",H13-H14-H18)</f>
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <f>IF(COUNTA(I13,I14,I18)&lt;3,"",I13-I14-I18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D21" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="D22" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D23" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="51" t="b">
-        <f>E13=E15</f>
-        <v>1</v>
-      </c>
-      <c r="F23" s="51" t="b">
-        <f>F13=F15</f>
-        <v>1</v>
-      </c>
-      <c r="G23" s="51" t="b">
-        <f>G13=G15</f>
-        <v>1</v>
-      </c>
-      <c r="H23" s="51" t="b">
-        <f>H13=H15</f>
-        <v>1</v>
-      </c>
-      <c r="I23" s="51"/>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="27"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="34"/>
-      <c r="B25" s="35"/>
-      <c r="D25">
-        <f>B5</f>
-        <v>0</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="46" t="str">
+        <f>IF(COUNTA(E13,E15)&lt;2,"",ABS(E13-E15)&lt;0.1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="46" t="str">
+        <f>IF(COUNTA(F13,F15)&lt;2,"",ABS(F13-F15)&lt;0.1)</f>
+        <v/>
+      </c>
+      <c r="G23" s="46" t="str">
+        <f>IF(COUNTA(G13,G15)&lt;2,"",ABS(G13-G15)&lt;0.1)</f>
+        <v/>
+      </c>
+      <c r="H23" s="46" t="str">
+        <f>IF(COUNTA(H13,H15)&lt;2,"",ABS(H13-H15)&lt;0.1)</f>
+        <v/>
+      </c>
+      <c r="I23" s="46" t="str">
+        <f>IF(COUNTA(I13,I15)&lt;2,"",ABS(I13-I15)&lt;0.1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="26"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="33"/>
+      <c r="B25" s="34"/>
+      <c r="D25" t="str">
+        <f>IF(B5="","",B5)</f>
+        <v/>
       </c>
       <c r="E25" t="str">
         <f>B4</f>
         <v>CAT</v>
       </c>
-      <c r="K25" s="52" t="s">
+      <c r="K25" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="L25" s="52"/>
-      <c r="M25" s="52"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="37"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="36"/>
       <c r="D26" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E26" s="5">
         <f>E2</f>
         <v>44561</v>
       </c>
       <c r="F26" s="5">
-        <f t="shared" ref="F26:I26" si="1">F2</f>
+        <f t="shared" ref="F26:I26" si="0">F2</f>
         <v>44926</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>45291</v>
       </c>
       <c r="H26" s="5">
-        <f t="shared" si="1"/>
-        <v>45656</v>
+        <f t="shared" si="0"/>
+        <v>45657</v>
       </c>
       <c r="I26" s="5">
-        <f t="shared" si="1"/>
-        <v>46021</v>
-      </c>
-      <c r="K26" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>46022</v>
+      </c>
+      <c r="K26" s="5" t="str">
         <f>K2</f>
-        <v>% ∆ 21 to 22</v>
-      </c>
-      <c r="L26" s="6" t="str">
-        <f t="shared" ref="L26:M26" si="2">L2</f>
-        <v>% ∆ 22 to 23</v>
-      </c>
-      <c r="M26" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>% ∆ 23 to 24</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="D27" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="41"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="42"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="35"/>
-      <c r="D28" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="42"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="43" t="s">
+        <v>2021 to 2022</v>
+      </c>
+      <c r="L26" s="5" t="str">
+        <f>L2</f>
+        <v>2022 to 2023</v>
+      </c>
+      <c r="M26" s="5" t="str">
+        <f>M2</f>
+        <v>2023 to 2024</v>
+      </c>
+      <c r="N26" s="5" t="str">
+        <f>N2</f>
+        <v>2024 to 2025</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="B29" s="44"/>
-      <c r="D29" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="42"/>
-    </row>
-    <row r="30" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
-      <c r="B30" s="46"/>
-      <c r="D30" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="41"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="42"/>
+      <c r="B27" s="38"/>
+      <c r="D27" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="55"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="57"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="74"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="33"/>
+      <c r="B28" s="34"/>
+      <c r="D28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="56"/>
+      <c r="F28" s="52"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="58"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="68"/>
+      <c r="M28" s="68"/>
+      <c r="N28" s="75"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="D29" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="56"/>
+      <c r="F29" s="52"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="58"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="75"/>
+    </row>
+    <row r="30" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="41"/>
+      <c r="B30" s="42"/>
+      <c r="D30" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30" s="60"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="62"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="68"/>
+      <c r="M30" s="68"/>
+      <c r="N30" s="75"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D31" s="54" t="s">
+        <v>53</v>
+      </c>
+      <c r="E31" s="64"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="66"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="76"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="D32" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="65"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="67"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="79"/>
+      <c r="M32" s="79"/>
+      <c r="N32" s="80"/>
+    </row>
+    <row r="34" spans="4:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D34" s="77" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="77"/>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+      <c r="I34" s="77"/>
+      <c r="J34" s="77"/>
+      <c r="K34" s="77"/>
+      <c r="L34" s="77"/>
+      <c r="M34" s="77"/>
+      <c r="N34" s="77"/>
+    </row>
+    <row r="35" spans="4:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="D35" s="44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="4:14" x14ac:dyDescent="0.2">
+      <c r="D36" s="44" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="4:14" x14ac:dyDescent="0.2">
+      <c r="D37" s="44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="4:14" x14ac:dyDescent="0.2">
+      <c r="D38" s="44" t="s">
+        <v>59</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
